--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.12581009174926</v>
+        <v>8.957944139909255</v>
       </c>
       <c r="D2" t="n">
-        <v>50.87278372034293</v>
+        <v>8.266827354555726</v>
       </c>
       <c r="E2" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F2" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.24423957375287</v>
+        <v>1.664688930734841</v>
       </c>
       <c r="D3" t="n">
-        <v>7.073340058105094</v>
+        <v>1.149417759442078</v>
       </c>
       <c r="E3" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F3" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>71.5938352061353</v>
+        <v>11.63399822099699</v>
       </c>
       <c r="D4" t="n">
-        <v>66.22446653115558</v>
+        <v>10.76147581131278</v>
       </c>
       <c r="E4" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F4" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3.030017749257456</v>
+        <v>0.4923778842543367</v>
       </c>
       <c r="D5" t="n">
-        <v>3.230699276816943</v>
+        <v>0.5249886324827533</v>
       </c>
       <c r="E5" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F5" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.18364410229897</v>
+        <v>8.642342166623584</v>
       </c>
       <c r="D6" t="n">
-        <v>46.99808526275803</v>
+        <v>7.637188855198181</v>
       </c>
       <c r="E6" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F6" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.70087712549569</v>
+        <v>0.9263925328930496</v>
       </c>
       <c r="D7" t="n">
-        <v>7.519917257228005</v>
+        <v>1.221986554299551</v>
       </c>
       <c r="E7" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F7" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.80773631397161</v>
+        <v>2.731257151020387</v>
       </c>
       <c r="D8" t="n">
-        <v>13.16913356950764</v>
+        <v>2.139984205044992</v>
       </c>
       <c r="E8" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F8" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>63.326463345862</v>
+        <v>10.29055029370258</v>
       </c>
       <c r="D9" t="n">
-        <v>54.91097392611387</v>
+        <v>8.923033262993505</v>
       </c>
       <c r="E9" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F9" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>15.43534904043313</v>
+        <v>2.508244219070384</v>
       </c>
       <c r="D10" t="n">
-        <v>9.435453236478775</v>
+        <v>1.533261150927801</v>
       </c>
       <c r="E10" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F10" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.60108568847501</v>
+        <v>3.83517642437719</v>
       </c>
       <c r="D11" t="n">
-        <v>19.82142499642468</v>
+        <v>3.220981561919011</v>
       </c>
       <c r="E11" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F11" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.50580864550941</v>
+        <v>3.494693904895279</v>
       </c>
       <c r="D12" t="n">
-        <v>19.50712586774396</v>
+        <v>3.169907953508393</v>
       </c>
       <c r="E12" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F12" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>69.36078157629582</v>
+        <v>11.27112700614807</v>
       </c>
       <c r="D13" t="n">
-        <v>50.23254321652554</v>
+        <v>8.1627882726854</v>
       </c>
       <c r="E13" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F13" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.61736452375714</v>
+        <v>4.975321735110534</v>
       </c>
       <c r="D14" t="n">
-        <v>27.91455215872579</v>
+        <v>4.536114725792941</v>
       </c>
       <c r="E14" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F14" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>3.032476997437017</v>
+        <v>0.4927775120835153</v>
       </c>
       <c r="D15" t="n">
-        <v>3.25262947647252</v>
+        <v>0.5285522899267846</v>
       </c>
       <c r="E15" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F15" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>16.46498692350529</v>
+        <v>2.675560375069609</v>
       </c>
       <c r="D16" t="n">
-        <v>16.21771643522352</v>
+        <v>2.635378920723821</v>
       </c>
       <c r="E16" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F16" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>32.07957022094793</v>
+        <v>5.212930160904039</v>
       </c>
       <c r="D17" t="n">
-        <v>22.17849199248207</v>
+        <v>3.604004948778336</v>
       </c>
       <c r="E17" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F17" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>39.6703659734376</v>
+        <v>6.446434470683611</v>
       </c>
       <c r="D18" t="n">
-        <v>36.20601071097962</v>
+        <v>5.883476740534189</v>
       </c>
       <c r="E18" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F18" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>25.71137253268355</v>
+        <v>4.178098036561076</v>
       </c>
       <c r="D19" t="n">
-        <v>25.96715060227551</v>
+        <v>4.21966197286977</v>
       </c>
       <c r="E19" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F19" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>47.89643789016539</v>
+        <v>7.783171157151877</v>
       </c>
       <c r="D20" t="n">
-        <v>33.20611052112593</v>
+        <v>5.395992959682964</v>
       </c>
       <c r="E20" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F20" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>22.96692481836523</v>
+        <v>3.732125282984349</v>
       </c>
       <c r="D21" t="n">
-        <v>23.15416517255337</v>
+        <v>3.762551840539923</v>
       </c>
       <c r="E21" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F21" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>39.33744836852192</v>
+        <v>6.392335359884812</v>
       </c>
       <c r="D22" t="n">
-        <v>32.45085994118543</v>
+        <v>5.273264740442634</v>
       </c>
       <c r="E22" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F22" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>29.82740918502558</v>
+        <v>4.846953992566656</v>
       </c>
       <c r="D23" t="n">
-        <v>29.53205427279941</v>
+        <v>4.798958819329905</v>
       </c>
       <c r="E23" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F23" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>20.35048491340595</v>
+        <v>3.306953798428467</v>
       </c>
       <c r="D24" t="n">
-        <v>20.0665109988695</v>
+        <v>3.260808037316293</v>
       </c>
       <c r="E24" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F24" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>26.3283845764864</v>
+        <v>4.27836249367904</v>
       </c>
       <c r="D25" t="n">
-        <v>26.38862220172663</v>
+        <v>4.288151107780577</v>
       </c>
       <c r="E25" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F25" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>43.62663552820828</v>
+        <v>7.089328273333846</v>
       </c>
       <c r="D26" t="n">
-        <v>43.26650256013671</v>
+        <v>7.030806666022215</v>
       </c>
       <c r="E26" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F26" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>43.25972967557804</v>
+        <v>7.029706072281432</v>
       </c>
       <c r="D27" t="n">
-        <v>42.89279575884837</v>
+        <v>6.970079310812861</v>
       </c>
       <c r="E27" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F27" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>42.73512194560004</v>
+        <v>6.944457316160007</v>
       </c>
       <c r="D28" t="n">
-        <v>42.8390181650708</v>
+        <v>6.961340451824006</v>
       </c>
       <c r="E28" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F28" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>37.8662379699123</v>
+        <v>6.153263670110749</v>
       </c>
       <c r="D29" t="n">
-        <v>37.49702257672801</v>
+        <v>6.093266168718301</v>
       </c>
       <c r="E29" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F29" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>42.00320813637617</v>
+        <v>6.825521322161127</v>
       </c>
       <c r="D30" t="n">
-        <v>41.71639884625796</v>
+        <v>6.778914812516919</v>
       </c>
       <c r="E30" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F30" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>36.68484035657111</v>
+        <v>5.961286557942805</v>
       </c>
       <c r="D31" t="n">
-        <v>36.42088199106993</v>
+        <v>5.918393323548864</v>
       </c>
       <c r="E31" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F31" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>25.20186141056642</v>
+        <v>4.095302479217044</v>
       </c>
       <c r="D32" t="n">
-        <v>25.04148858994381</v>
+        <v>4.069241895865869</v>
       </c>
       <c r="E32" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F32" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>34.5036436698147</v>
+        <v>5.606842096344889</v>
       </c>
       <c r="D33" t="n">
-        <v>34.16417968083055</v>
+        <v>5.551679198134964</v>
       </c>
       <c r="E33" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F33" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>36.58105645357927</v>
+        <v>5.944421673706632</v>
       </c>
       <c r="D34" t="n">
-        <v>36.58658516093766</v>
+        <v>5.94532008865237</v>
       </c>
       <c r="E34" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F34" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>24.03296443880395</v>
+        <v>3.905356721305643</v>
       </c>
       <c r="D35" t="n">
-        <v>23.67047914749575</v>
+        <v>3.846452861468059</v>
       </c>
       <c r="E35" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F35" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>66.37708396115356</v>
+        <v>10.78627614368745</v>
       </c>
       <c r="D36" t="n">
-        <v>66.47271744750282</v>
+        <v>10.80181658521921</v>
       </c>
       <c r="E36" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F36" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>23.32667761860435</v>
+        <v>3.790585113023206</v>
       </c>
       <c r="D37" t="n">
-        <v>23.03197001117882</v>
+        <v>3.742695126816559</v>
       </c>
       <c r="E37" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F37" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>68.3543470536722</v>
+        <v>11.10758139622173</v>
       </c>
       <c r="D38" t="n">
-        <v>68.42889760117673</v>
+        <v>11.11969586019122</v>
       </c>
       <c r="E38" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F38" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>57.53085992544723</v>
+        <v>9.348764737885176</v>
       </c>
       <c r="D39" t="n">
-        <v>57.5323182313868</v>
+        <v>9.349001712600355</v>
       </c>
       <c r="E39" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F39" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>57.37647904947903</v>
+        <v>9.323677845540344</v>
       </c>
       <c r="D40" t="n">
-        <v>57.52503224260553</v>
+        <v>9.3478177394234</v>
       </c>
       <c r="E40" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F40" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>74.45596471347103</v>
+        <v>12.09909426593904</v>
       </c>
       <c r="D41" t="n">
-        <v>74.51834948053354</v>
+        <v>12.1092317905867</v>
       </c>
       <c r="E41" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F41" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>21.2389306826144</v>
+        <v>3.451326235924839</v>
       </c>
       <c r="D42" t="n">
-        <v>21.10773340132357</v>
+        <v>3.430006677715081</v>
       </c>
       <c r="E42" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F42" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>13.29114079849809</v>
+        <v>2.15981037975594</v>
       </c>
       <c r="D43" t="n">
-        <v>12.91888570987301</v>
+        <v>2.099318927854364</v>
       </c>
       <c r="E43" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F43" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>10.10678458219268</v>
+        <v>1.64235249460631</v>
       </c>
       <c r="D44" t="n">
-        <v>9.954753584913314</v>
+        <v>1.617647457548414</v>
       </c>
       <c r="E44" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F44" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>85.86050777677076</v>
+        <v>13.95233251372525</v>
       </c>
       <c r="D45" t="n">
-        <v>85.93001974870808</v>
+        <v>13.96362820916506</v>
       </c>
       <c r="E45" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F45" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>3.30903810031545</v>
+        <v>0.5377186913012606</v>
       </c>
       <c r="D46" t="n">
-        <v>3.258332684296493</v>
+        <v>0.5294790611981802</v>
       </c>
       <c r="E46" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F46" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>73.20289594766601</v>
+        <v>11.89547059149573</v>
       </c>
       <c r="D47" t="n">
-        <v>73.18955711044354</v>
+        <v>11.89330303044708</v>
       </c>
       <c r="E47" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F47" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>30.4031498564579</v>
+        <v>4.940511851674409</v>
       </c>
       <c r="D48" t="n">
-        <v>30.43386525731826</v>
+        <v>4.945503104314217</v>
       </c>
       <c r="E48" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F48" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>69.17390543658776</v>
+        <v>11.24075963344551</v>
       </c>
       <c r="D49" t="n">
-        <v>69.07553303583805</v>
+        <v>11.22477411832368</v>
       </c>
       <c r="E49" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F49" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>69.20393949164686</v>
+        <v>11.24564016739262</v>
       </c>
       <c r="D50" t="n">
-        <v>69.07593682598427</v>
+        <v>11.22483973422244</v>
       </c>
       <c r="E50" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F50" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>7.932988686501541</v>
+        <v>1.2891106615565</v>
       </c>
       <c r="D51" t="n">
-        <v>8.212844164021821</v>
+        <v>1.334587176653546</v>
       </c>
       <c r="E51" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F51" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>17.98474362188857</v>
+        <v>2.922520838556892</v>
       </c>
       <c r="D52" t="n">
-        <v>18.06970827732107</v>
+        <v>2.936327595064673</v>
       </c>
       <c r="E52" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F52" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>75.58607154164085</v>
+        <v>12.28273662551664</v>
       </c>
       <c r="D53" t="n">
-        <v>75.46419445441788</v>
+        <v>12.26293159884291</v>
       </c>
       <c r="E53" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F53" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>74.39744303634509</v>
+        <v>12.08958449340608</v>
       </c>
       <c r="D54" t="n">
-        <v>74.45304405852032</v>
+        <v>12.09861965950955</v>
       </c>
       <c r="E54" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F54" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>81.682303275035</v>
+        <v>13.27337428219319</v>
       </c>
       <c r="D55" t="n">
-        <v>81.61610453539647</v>
+        <v>13.26261698700193</v>
       </c>
       <c r="E55" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F55" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>11.02329850517273</v>
+        <v>1.791286007090569</v>
       </c>
       <c r="D56" t="n">
-        <v>11.39831280874893</v>
+        <v>1.852225831421701</v>
       </c>
       <c r="E56" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F56" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>98.87594601592001</v>
+        <v>16.067341227587</v>
       </c>
       <c r="D57" t="n">
-        <v>98.91082656560963</v>
+        <v>16.07300931691157</v>
       </c>
       <c r="E57" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F57" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>81.74157979536203</v>
+        <v>13.28300671674633</v>
       </c>
       <c r="D58" t="n">
-        <v>81.59982138664674</v>
+        <v>13.25997097533009</v>
       </c>
       <c r="E58" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F58" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>81.09649474753351</v>
+        <v>13.1781803964742</v>
       </c>
       <c r="D59" t="n">
-        <v>80.99518764602105</v>
+        <v>13.16171799247842</v>
       </c>
       <c r="E59" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F59" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>68.25739154283802</v>
+        <v>11.09182612571118</v>
       </c>
       <c r="D60" t="n">
-        <v>68.34549474327139</v>
+        <v>11.1061428957816</v>
       </c>
       <c r="E60" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F60" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>19.35778427710088</v>
+        <v>3.145639945028893</v>
       </c>
       <c r="D61" t="n">
-        <v>19.70689759578919</v>
+        <v>3.202370859315744</v>
       </c>
       <c r="E61" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F61" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>59.02754808767828</v>
+        <v>9.591976564247719</v>
       </c>
       <c r="D62" t="n">
-        <v>59.12158849975098</v>
+        <v>9.607258131209534</v>
       </c>
       <c r="E62" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F62" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>89.00035831418134</v>
+        <v>14.46255822605447</v>
       </c>
       <c r="D63" t="n">
-        <v>88.92689066136838</v>
+        <v>14.45061973247236</v>
       </c>
       <c r="E63" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F63" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>100.6455027331573</v>
+        <v>16.35489419413807</v>
       </c>
       <c r="D64" t="n">
-        <v>100.639227016848</v>
+        <v>16.35387439023779</v>
       </c>
       <c r="E64" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F64" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2496,16 +2496,16 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>25.99585171460669</v>
+        <v>4.224325903623587</v>
       </c>
       <c r="D65" t="n">
-        <v>26.37117563743798</v>
+        <v>4.285316041083671</v>
       </c>
       <c r="E65" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F65" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2528,16 +2528,16 @@
         <v>65</v>
       </c>
       <c r="C66" t="n">
-        <v>82.79444846489801</v>
+        <v>13.45409787554593</v>
       </c>
       <c r="D66" t="n">
-        <v>82.8976659438291</v>
+        <v>13.47087071587223</v>
       </c>
       <c r="E66" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F66" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2560,16 +2560,16 @@
         <v>66</v>
       </c>
       <c r="C67" t="n">
-        <v>97.53632170759518</v>
+        <v>15.84965227748422</v>
       </c>
       <c r="D67" t="n">
-        <v>97.4513460292594</v>
+        <v>15.83584372975465</v>
       </c>
       <c r="E67" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F67" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2592,16 +2592,16 @@
         <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>112.1046019905896</v>
+        <v>18.21699782347081</v>
       </c>
       <c r="D68" t="n">
-        <v>112.1142039823747</v>
+        <v>18.21855814713588</v>
       </c>
       <c r="E68" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F68" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2624,16 +2624,16 @@
         <v>68</v>
       </c>
       <c r="C69" t="n">
-        <v>58.27681428930849</v>
+        <v>9.46998232201263</v>
       </c>
       <c r="D69" t="n">
-        <v>58.47170438788674</v>
+        <v>9.501651963031595</v>
       </c>
       <c r="E69" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F69" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2656,16 +2656,16 @@
         <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>34.92345724336487</v>
+        <v>5.675061802046792</v>
       </c>
       <c r="D70" t="n">
-        <v>35.28037773450942</v>
+        <v>5.733061381857781</v>
       </c>
       <c r="E70" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F70" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2688,16 +2688,16 @@
         <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>81.23199013823931</v>
+        <v>13.20019839746389</v>
       </c>
       <c r="D71" t="n">
-        <v>81.37485780518128</v>
+        <v>13.22341439334196</v>
       </c>
       <c r="E71" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F71" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2720,16 +2720,16 @@
         <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>108.0593194988728</v>
+        <v>17.55963941856683</v>
       </c>
       <c r="D72" t="n">
-        <v>108.0269021787066</v>
+        <v>17.55437160403983</v>
       </c>
       <c r="E72" t="n">
-        <v>28.84789353003057</v>
+        <v>4.687782698629967</v>
       </c>
       <c r="F72" t="n">
-        <v>29.01132993891425</v>
+        <v>4.714341115073567</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
